--- a/1-code/ruwen/figure/network_table_i.xlsx
+++ b/1-code/ruwen/figure/network_table_i.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qd/Desktop/helios/HELIOS-project/1-code/ruwen/figure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5078953-E5EE-AF47-9BF7-2F3AEE2A65D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC81E7F3-79AA-8C47-A488-5A51B1168F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="25540" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1580" yWindow="500" windowWidth="25540" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="136">
   <si>
     <t>from</t>
   </si>
@@ -422,6 +422,14 @@
   </si>
   <si>
     <t>Zinc</t>
+  </si>
+  <si>
+    <t>Eubacterium limosum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Veillonella rogosae</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -457,12 +465,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -477,12 +491,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2015,264 +2030,264 @@
         <v>1.9458758772910629</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:9" s="3" customFormat="1">
+      <c r="A43" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="3">
         <v>-0.4806234086726725</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="3">
         <v>1.534152339570701E-2</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H43" s="2">
+      <c r="G43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="3">
         <v>0.4806234086726725</v>
       </c>
-      <c r="I43" s="2">
+      <c r="I43" s="3">
         <v>1.814131513300985</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:9" s="3" customFormat="1">
+      <c r="A44" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="3">
         <v>-0.4770719075870718</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>1.6308116284636801E-2</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H44" s="2">
+      <c r="G44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="3">
         <v>0.4770719075870718</v>
       </c>
-      <c r="I44" s="2">
+      <c r="I44" s="3">
         <v>1.787596200482326</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:9" s="3" customFormat="1">
+      <c r="A45" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="3">
         <v>0.5377100094752929</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
         <v>5.221442540377842E-3</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H45" s="2">
+      <c r="G45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" s="3">
         <v>0.5377100094752929</v>
       </c>
-      <c r="I45" s="2">
+      <c r="I45" s="3">
         <v>2.2822094968487958</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:9" s="3" customFormat="1">
+      <c r="A46" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="3">
         <v>0.52324057296603954</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="3">
         <v>6.9782530308944131E-3</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H46" s="2">
+      <c r="G46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" s="3">
         <v>0.52324057296603954</v>
       </c>
-      <c r="I46" s="2">
+      <c r="I46" s="3">
         <v>2.1562532871193678</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:9" s="3" customFormat="1">
+      <c r="A47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="3">
         <v>-0.4934556311428358</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
         <v>1.2231297927191419E-2</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H47" s="2">
+      <c r="G47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="3">
         <v>0.4934556311428358</v>
       </c>
-      <c r="I47" s="2">
+      <c r="I47" s="3">
         <v>1.912527455252478</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:9" s="3" customFormat="1">
+      <c r="A48" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="3">
         <v>-0.51077143142574577</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="3">
         <v>8.9014043878492509E-3</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H48" s="2">
+      <c r="G48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="3">
         <v>0.51077143142574577</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I48" s="3">
         <v>2.0505414686610401</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:9" s="3" customFormat="1">
+      <c r="A49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="3">
         <v>-0.48187921758502972</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
         <v>1.5010686890649629E-2</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H49" s="2">
+      <c r="G49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="3">
         <v>0.48187921758502972</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="3">
         <v>1.8235994339397219</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:9" s="3" customFormat="1">
+      <c r="A50" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="3">
         <v>-0.53265329565651975</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="3">
         <v>5.7851091109107026E-3</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" s="2">
+      <c r="G50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="3">
         <v>0.53265329565651975</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I50" s="3">
         <v>2.2376884455593249</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:9" s="3" customFormat="1">
+      <c r="A51" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="3">
         <v>-0.47370920214994727</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="3">
         <v>1.7298401929823331E-2</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H51" s="2">
+      <c r="G51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" s="3">
         <v>0.47370920214994727</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I51" s="3">
         <v>1.7619940162421119</v>
       </c>
     </row>
@@ -3204,61 +3219,61 @@
         <v>1.8050603191904699</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
-      <c r="A84" s="2" t="s">
+    <row r="84" spans="1:9" s="3" customFormat="1">
+      <c r="A84" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C84" s="3">
+        <v>-0.48335456236691471</v>
+      </c>
+      <c r="D84" s="3">
+        <v>1.4633183696389419E-2</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="F84" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C84" s="2">
-        <v>-0.48335456236691471</v>
-      </c>
-      <c r="D84" s="2">
-        <v>1.4633183696389419E-2</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F84" s="2" t="s">
+      <c r="G84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="3">
+        <v>0.48335456236691471</v>
+      </c>
+      <c r="I84" s="3">
+        <v>1.83466117549107</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" s="3" customFormat="1">
+      <c r="A85" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H84" s="2">
-        <v>0.48335456236691471</v>
-      </c>
-      <c r="I84" s="2">
-        <v>1.83466117549107</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85" s="2" t="s">
+      <c r="C85" s="3">
+        <v>0.4683667615217485</v>
+      </c>
+      <c r="D85" s="3">
+        <v>1.8936001837296448E-2</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F85" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C85" s="2">
+      <c r="G85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H85" s="3">
         <v>0.4683667615217485</v>
       </c>
-      <c r="D85" s="2">
-        <v>1.8936001837296448E-2</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H85" s="2">
-        <v>0.4683667615217485</v>
-      </c>
-      <c r="I85" s="2">
+      <c r="I85" s="3">
         <v>1.722711712940842</v>
       </c>
     </row>
